--- a/admin.xlsx
+++ b/admin.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rubat\Downloads\bde-site-v8-dossier-events-data-guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F894D9-5A2B-4F27-9047-D88F37CCE3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C227DF3-4D37-4189-90E9-556FB783BE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LÉGENDE" sheetId="1" r:id="rId1"/>
@@ -1992,7 +1992,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2009,6 +2009,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5653,12 +5662,13 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="4" width="70" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="75.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="69.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>301</v>
       </c>
@@ -5672,11 +5682,11 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
@@ -5686,11 +5696,11 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="13">
         <v>1</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -5700,11 +5710,11 @@
         <v>307</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -5714,11 +5724,11 @@
         <v>309</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="13">
         <v>1</v>
       </c>
       <c r="C5" s="10" t="s">
@@ -5728,11 +5738,11 @@
         <v>311</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="12">
         <v>1</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -5742,11 +5752,11 @@
         <v>313</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="13">
         <v>1</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -5756,11 +5766,11 @@
         <v>315</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="12">
         <v>2</v>
       </c>
       <c r="C8" s="9" t="s">
@@ -5770,11 +5780,11 @@
         <v>317</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="13">
         <v>1</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -5784,11 +5794,11 @@
         <v>319</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="12">
         <v>1</v>
       </c>
       <c r="C10" s="9" t="s">
